--- a/yuyang_retail_orders_fy_2025-05-01_2026-04-30.xlsx
+++ b/yuyang_retail_orders_fy_2025-05-01_2026-04-30.xlsx
@@ -3769,7 +3769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3780,6 +3780,7 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3823,6 +3824,11 @@
           <t>时间</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3859,6 +3865,11 @@
           <t>10:50:48</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>苍杰（个人）</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3895,6 +3906,11 @@
           <t>17:25:34</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>苍杰（个人）</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3931,6 +3947,11 @@
           <t>21:04:50</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>苍杰（个人）</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3967,6 +3988,11 @@
           <t>21:23:05</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>苍杰（个人）</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4003,6 +4029,11 @@
           <t>21:26:47</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>苍杰（个人）</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4039,6 +4070,11 @@
           <t>21:49:12</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>苍杰（个人）</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4073,6 +4109,11 @@
       <c r="H8" t="inlineStr">
         <is>
           <t>21:51:41</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>苍杰（个人）</t>
         </is>
       </c>
     </row>
